--- a/data/trans_bre/IP07B_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP07B_R2-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,177 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4,42</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,25</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-10,94</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>101,28%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>166,93%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>4.415666114760858</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.398255574839184</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.247737572718847</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-10.94412976341536</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1.012781695249889</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1.669338823206412</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1,43; 12,03</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-2,77; 6,92</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-3,13; 15,49</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-33,18; 0,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1.43173714647625</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.771153660439559</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.126284069362997</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-33.17593334969494</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>12.03469017460804</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.924400663742968</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>15.4857654708086</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,97</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,45</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-7,48%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-39,23%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>53,86%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>33,97%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,27; 2,25</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,07; 1,09</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,51; 1,81</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-1,42; 2,95</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-78,89; 304,1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-76,81; 43,34</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.1479164051979856</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.970809084096135</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.4463591903549693</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.3567503766594884</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.07479669547754791</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.3922686912807608</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.5385976275556368</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.3396749434466996</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-1,65</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,01</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,2</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-54,86%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-77,48%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.265611566113418</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.072507391312478</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.510448580708758</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-1.421127103573137</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.7889247076506856</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.7680953882113127</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-8,08; 2,48</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,3; 10,6</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-8,74; 0,49</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,5</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.246340983466768</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.093734795190272</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.805529336720045</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.953239274918625</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>3.041026389415838</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.4334247595015662</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,44 +797,32 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,28</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>15,23%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-12,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-8,41%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-8,61%</t>
+      <c r="C10" s="5" t="n">
+        <v>-1.651570937810231</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>4.010631309322531</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-3.2036283462205</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.519844501864491</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.5486158611657922</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.774805577530475</v>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -955,52 +830,152 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,57; 2,44</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,83; 1,94</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,87; 1,49</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-2,27; 1,68</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-62,28; 238,28</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-58,81; 83,02</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-71,16; 184,35</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 282,38</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-8.078140847029916</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1.296731701900509</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-8.737579356506767</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.482241299232427</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>10.59575614880957</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.4900368085604029</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>6.504229858445252</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.2839642999543139</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.4479617256320623</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.1431068327300781</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.1253895486138853</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1522837378403357</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1228768053861659</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.08412222187683181</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.08607058836357369</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.5667290888949</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.8266818738968</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.866977084903392</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-2.265197276176746</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.6227929288818084</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5880776911383191</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.7115841398245444</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.439829687839148</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.937722399442161</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.49285524139396</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.682598887999257</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>2.382792856701301</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.8302012717837844</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.843535158006919</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>2.823813403698435</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +983,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
